--- a/docs/STAFF-DATA/012.xlsx
+++ b/docs/STAFF-DATA/012.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Velammal-Engineering-College-Backend\docs\STAFF-DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\VEC_Web_Engine\docs\STAFF-DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1BDCF2-4CF1-4E53-9B4E-0702EBBDC666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="15036" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="15036" windowHeight="12336"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="116">
   <si>
     <t>Name</t>
   </si>
@@ -73,24 +72,9 @@
     <t>VEC-012-01-096</t>
   </si>
   <si>
-    <t>Mrs. BAKIALAKSHMI S</t>
-  </si>
-  <si>
     <t>Assistant Professor</t>
   </si>
   <si>
-    <t>/static/images/profile_photos/012/VEC-012-04-053.webp</t>
-  </si>
-  <si>
-    <t>https://scholar.google.co.in/citations?view_op=list_works&amp;hl=en&amp;user=gQw-z7MAAAAJ&amp;gmla=ALUCkoV7VrgXU1hRA9QyRDxH_mJ99V2VU6jFQEDls-Ell2tHQtOdN7WaQTJ09-kiZiTIdNH_a2q0TX8yuSnjzWIV7DH5aMzBnyPIRTBa9RcsCtld8LJoNg</t>
-  </si>
-  <si>
-    <t>linkedin.com/in/bakialakshmi-s-615670204</t>
-  </si>
-  <si>
-    <t>VEC-012-04-053</t>
-  </si>
-  <si>
     <t>Mr. BALU M S</t>
   </si>
   <si>
@@ -362,13 +346,34 @@
   </si>
   <si>
     <t>Mr. GOPIKRISHNAN S</t>
+  </si>
+  <si>
+    <t>Dr. ISWARYA M</t>
+  </si>
+  <si>
+    <t>/static/images/profile_photos/012/VEC-012-04-653.webp</t>
+  </si>
+  <si>
+    <t>VEC-012-04-653</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=lIcQEhoAAAAJ&amp;hl=en</t>
+  </si>
+  <si>
+    <t> https://www.researchgate.net/profile/Iswarya-Manickam</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/iswarya-manickam-814970371/</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-1420-8094</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,6 +394,21 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -430,10 +450,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -444,8 +465,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -745,7 +776,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
@@ -756,11 +787,11 @@
     <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="79.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.5546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" customWidth="1"/>
     <col min="8" max="8" width="35.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" style="2" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.5546875" style="2" customWidth="1"/>
     <col min="10" max="10" width="76" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -798,7 +829,7 @@
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -824,198 +855,198 @@
     </row>
     <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="H3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="J3" t="s">
         <v>30</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" t="s">
         <v>21</v>
-      </c>
-      <c r="J6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="J7" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
         <v>48</v>
       </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="E9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J9" t="s">
         <v>51</v>
       </c>
-      <c r="J8" t="s">
+    </row>
+    <row r="10" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>113</v>
-      </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="I10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" t="s">
         <v>55</v>
-      </c>
-      <c r="J10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
         <v>57</v>
       </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="I11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" t="s">
         <v>59</v>
-      </c>
-      <c r="J11" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
         <v>61</v>
       </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -1025,174 +1056,188 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>67</v>
       </c>
+      <c r="E13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="I13" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="J14" t="s">
-        <v>78</v>
+    </row>
+    <row r="14" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="I15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="J15" t="s">
         <v>81</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J15" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="J16" t="s">
         <v>88</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J16" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="J17" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="I18" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="J18" t="s">
         <v>100</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J18" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="J19" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D14" r:id="rId1"/>
+    <hyperlink ref="E14" r:id="rId2" display="https://www.researchgate.net/profile/Iswarya-Manickam"/>
+    <hyperlink ref="I14" r:id="rId3"/>
+    <hyperlink ref="F14" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>